--- a/public/templates/examples/A-126-EncryptionImplementationVerificationRecords-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-126-EncryptionImplementationVerificationRecords-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -186,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -243,6 +248,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +639,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="8" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -695,7 +703,7 @@
       <c r="E6" s="21" t="n"/>
       <c r="F6" s="20" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Verification cycle / scope</t>
@@ -722,7 +730,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Ref #</t>
@@ -790,10 +798,8 @@
           <t>Automated scan</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="F12" s="23">
+        <v>46048</v>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
@@ -828,10 +834,8 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="F13" s="23">
+        <v>46048</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
@@ -866,10 +870,8 @@
           <t>Config review</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="F14" s="23">
+        <v>46048</v>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
@@ -904,10 +906,8 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="F15" s="23">
+        <v>46048</v>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="H15" s="19" t="inlineStr"/>
     </row>
-    <row r="16" ht="19.5" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>EV-05</t>
@@ -942,10 +942,8 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="F16" s="23">
+        <v>46048</v>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
@@ -954,7 +952,7 @@
       </c>
       <c r="H16" s="19" t="inlineStr"/>
     </row>
-    <row r="17" ht="19.5" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>EV-06</t>
@@ -980,10 +978,8 @@
           <t>Confirmed with State ISO</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
+      <c r="F17" s="23">
+        <v>46048</v>
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="82.2" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Reviewed by: Information Security Analyst</t>
@@ -1106,7 +1102,7 @@
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
     </row>
-    <row r="30" ht="51" customHeight="1">
+    <row r="30" ht="66.4" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Approved by: Executive Director</t>
@@ -1220,7 +1216,7 @@
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="12" t="n"/>
     </row>
-    <row r="46" ht="17" customHeight="1">
+    <row r="46" ht="34.7" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1245,11 +1241,11 @@
       <c r="F46" s="11" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -1272,7 +1268,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:B4"/>
@@ -1281,7 +1276,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>